--- a/cowork-copilot/Contoso_Fargo_GoLive_Readiness_Tracker.xlsx
+++ b/cowork-copilot/Contoso_Fargo_GoLive_Readiness_Tracker.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
@@ -583,7 +583,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
@@ -623,7 +623,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Kai</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Kai</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
@@ -743,7 +743,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Kai</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
@@ -783,7 +783,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="E9" s="1" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="E10" s="1" t="n">
@@ -895,7 +895,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="E11" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="E12" s="1" t="n">

--- a/cowork-copilot/Contoso_Fargo_GoLive_Readiness_Tracker.xlsx
+++ b/cowork-copilot/Contoso_Fargo_GoLive_Readiness_Tracker.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
@@ -583,7 +583,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
@@ -623,7 +623,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>Vance</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>Vance</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
@@ -743,7 +743,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>Vance</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
@@ -895,7 +895,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="E11" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="E12" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Billie</t>
         </is>
       </c>
       <c r="E13" s="1" t="n">
